--- a/WEB-INF/templateFile/ChiChinginkeisansho.xlsx
+++ b/WEB-INF/templateFile/ChiChinginkeisansho.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.200.3\0-546-0\勤怠管理システム\01_成果物\00_帳票テンプレート\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\Kintai\workspace\Kintai\WEB-INF\templateFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1E3F1E0-0BA4-4B93-BC26-C21A7369A5DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17025" windowHeight="11535"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,6 +23,9 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -301,7 +305,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -521,25 +525,16 @@
     <xf numFmtId="20" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="20" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -563,6 +558,9 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="38" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -572,7 +570,19 @@
     <xf numFmtId="38" fontId="5" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -593,19 +603,13 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -888,83 +892,83 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BC52"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="2" width="2.625" style="1" customWidth="1"/>
-    <col min="3" max="6" width="2.125" style="1" customWidth="1"/>
-    <col min="7" max="35" width="2.625" style="1" customWidth="1"/>
-    <col min="36" max="43" width="2.125" style="1" customWidth="1"/>
-    <col min="44" max="46" width="2.625" style="1" customWidth="1"/>
-    <col min="47" max="55" width="2.125" style="1" customWidth="1"/>
+    <col min="1" max="2" width="2.59765625" style="1" customWidth="1"/>
+    <col min="3" max="6" width="2.09765625" style="1" customWidth="1"/>
+    <col min="7" max="35" width="2.59765625" style="1" customWidth="1"/>
+    <col min="36" max="43" width="2.09765625" style="1" customWidth="1"/>
+    <col min="44" max="46" width="2.59765625" style="1" customWidth="1"/>
+    <col min="47" max="55" width="2.09765625" style="1" customWidth="1"/>
     <col min="56" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:55" ht="45" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="54" t="s">
+    <row r="1" spans="1:55" ht="45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="54"/>
-      <c r="O1" s="54"/>
-      <c r="P1" s="54"/>
-      <c r="Q1" s="54"/>
-      <c r="R1" s="54"/>
-      <c r="S1" s="54"/>
-      <c r="T1" s="54"/>
-      <c r="U1" s="54"/>
-      <c r="V1" s="54"/>
-      <c r="W1" s="54"/>
-      <c r="X1" s="54"/>
-      <c r="Y1" s="54"/>
-      <c r="Z1" s="54"/>
-      <c r="AA1" s="54"/>
-      <c r="AB1" s="54"/>
-      <c r="AC1" s="54"/>
-      <c r="AD1" s="54"/>
-      <c r="AE1" s="54"/>
-      <c r="AF1" s="54"/>
-      <c r="AG1" s="54"/>
-      <c r="AH1" s="54"/>
-      <c r="AI1" s="54"/>
-      <c r="AJ1" s="54"/>
-      <c r="AK1" s="54"/>
-      <c r="AL1" s="54"/>
-      <c r="AM1" s="54"/>
-      <c r="AN1" s="54"/>
-      <c r="AO1" s="54"/>
-      <c r="AP1" s="54"/>
-      <c r="AQ1" s="54"/>
-      <c r="AR1" s="54"/>
-      <c r="AS1" s="54"/>
-      <c r="AT1" s="54"/>
-      <c r="AU1" s="54"/>
-      <c r="AV1" s="54"/>
-      <c r="AW1" s="54"/>
-      <c r="AX1" s="54"/>
-      <c r="AY1" s="54"/>
-      <c r="AZ1" s="54"/>
-      <c r="BA1" s="54"/>
-      <c r="BB1" s="54"/>
-      <c r="BC1" s="54"/>
-    </row>
-    <row r="2" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="3" spans="1:55" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="45"/>
+      <c r="Q1" s="45"/>
+      <c r="R1" s="45"/>
+      <c r="S1" s="45"/>
+      <c r="T1" s="45"/>
+      <c r="U1" s="45"/>
+      <c r="V1" s="45"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
+      <c r="AB1" s="45"/>
+      <c r="AC1" s="45"/>
+      <c r="AD1" s="45"/>
+      <c r="AE1" s="45"/>
+      <c r="AF1" s="45"/>
+      <c r="AG1" s="45"/>
+      <c r="AH1" s="45"/>
+      <c r="AI1" s="45"/>
+      <c r="AJ1" s="45"/>
+      <c r="AK1" s="45"/>
+      <c r="AL1" s="45"/>
+      <c r="AM1" s="45"/>
+      <c r="AN1" s="45"/>
+      <c r="AO1" s="45"/>
+      <c r="AP1" s="45"/>
+      <c r="AQ1" s="45"/>
+      <c r="AR1" s="45"/>
+      <c r="AS1" s="45"/>
+      <c r="AT1" s="45"/>
+      <c r="AU1" s="45"/>
+      <c r="AV1" s="45"/>
+      <c r="AW1" s="45"/>
+      <c r="AX1" s="45"/>
+      <c r="AY1" s="45"/>
+      <c r="AZ1" s="45"/>
+      <c r="BA1" s="45"/>
+      <c r="BB1" s="45"/>
+      <c r="BC1" s="45"/>
+    </row>
+    <row r="2" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="3" spans="1:55" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -985,90 +989,90 @@
       <c r="R3" s="7"/>
       <c r="S3" s="7"/>
       <c r="T3" s="7"/>
-      <c r="AR3" s="50"/>
-      <c r="AS3" s="50"/>
-      <c r="AT3" s="50"/>
-      <c r="AU3" s="50"/>
-      <c r="AV3" s="50"/>
-      <c r="AW3" s="50"/>
-      <c r="AX3" s="51"/>
-      <c r="AY3" s="51"/>
-      <c r="AZ3" s="51"/>
-      <c r="BA3" s="51"/>
-      <c r="BB3" s="51"/>
-      <c r="BC3" s="51"/>
-    </row>
-    <row r="4" spans="1:55" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="36"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
-      <c r="AR4" s="53"/>
-      <c r="AS4" s="53"/>
-      <c r="AT4" s="53"/>
-      <c r="AU4" s="53"/>
-      <c r="AV4" s="53"/>
-      <c r="AW4" s="53"/>
-      <c r="AX4" s="53"/>
-      <c r="AY4" s="53"/>
-      <c r="AZ4" s="53"/>
-      <c r="BA4" s="53"/>
-      <c r="BB4" s="53"/>
-      <c r="BC4" s="53"/>
-    </row>
-    <row r="5" spans="1:55" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="36"/>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="36"/>
-      <c r="K5" s="52"/>
-      <c r="L5" s="36"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="36"/>
-      <c r="Q5" s="36"/>
-      <c r="R5" s="36"/>
-      <c r="S5" s="36"/>
-      <c r="T5" s="36"/>
-      <c r="U5" s="36"/>
-      <c r="AJ5" s="47" t="s">
+      <c r="AR3" s="41"/>
+      <c r="AS3" s="41"/>
+      <c r="AT3" s="41"/>
+      <c r="AU3" s="41"/>
+      <c r="AV3" s="41"/>
+      <c r="AW3" s="41"/>
+      <c r="AX3" s="42"/>
+      <c r="AY3" s="42"/>
+      <c r="AZ3" s="42"/>
+      <c r="BA3" s="42"/>
+      <c r="BB3" s="42"/>
+      <c r="BC3" s="42"/>
+    </row>
+    <row r="4" spans="1:55" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="33"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33"/>
+      <c r="AR4" s="44"/>
+      <c r="AS4" s="44"/>
+      <c r="AT4" s="44"/>
+      <c r="AU4" s="44"/>
+      <c r="AV4" s="44"/>
+      <c r="AW4" s="44"/>
+      <c r="AX4" s="44"/>
+      <c r="AY4" s="44"/>
+      <c r="AZ4" s="44"/>
+      <c r="BA4" s="44"/>
+      <c r="BB4" s="44"/>
+      <c r="BC4" s="44"/>
+    </row>
+    <row r="5" spans="1:55" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="33"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="33"/>
+      <c r="K5" s="43"/>
+      <c r="L5" s="33"/>
+      <c r="M5" s="33"/>
+      <c r="N5" s="33"/>
+      <c r="O5" s="33"/>
+      <c r="P5" s="33"/>
+      <c r="Q5" s="33"/>
+      <c r="R5" s="33"/>
+      <c r="S5" s="33"/>
+      <c r="T5" s="33"/>
+      <c r="U5" s="33"/>
+      <c r="AJ5" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="AK5" s="48"/>
-      <c r="AL5" s="48"/>
-      <c r="AM5" s="49"/>
-      <c r="AN5" s="44"/>
-      <c r="AO5" s="45"/>
-      <c r="AP5" s="45"/>
-      <c r="AQ5" s="46"/>
-      <c r="AR5" s="36"/>
-      <c r="AS5" s="36"/>
-      <c r="AT5" s="36"/>
-      <c r="AU5" s="36"/>
-      <c r="AV5" s="36"/>
-      <c r="AW5" s="36"/>
-      <c r="AX5" s="36"/>
-      <c r="AY5" s="36"/>
-      <c r="AZ5" s="36"/>
-      <c r="BA5" s="36"/>
-      <c r="BB5" s="36"/>
-      <c r="BC5" s="36"/>
-    </row>
-    <row r="6" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="7" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AK5" s="50"/>
+      <c r="AL5" s="50"/>
+      <c r="AM5" s="51"/>
+      <c r="AN5" s="46"/>
+      <c r="AO5" s="47"/>
+      <c r="AP5" s="47"/>
+      <c r="AQ5" s="48"/>
+      <c r="AR5" s="33"/>
+      <c r="AS5" s="33"/>
+      <c r="AT5" s="33"/>
+      <c r="AU5" s="33"/>
+      <c r="AV5" s="33"/>
+      <c r="AW5" s="33"/>
+      <c r="AX5" s="33"/>
+      <c r="AY5" s="33"/>
+      <c r="AZ5" s="33"/>
+      <c r="BA5" s="33"/>
+      <c r="BB5" s="33"/>
+      <c r="BC5" s="33"/>
+    </row>
+    <row r="6" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="7" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="15" t="s">
         <v>25</v>
       </c>
@@ -1081,19 +1085,19 @@
       <c r="H7" s="15"/>
       <c r="I7" s="15"/>
       <c r="J7" s="15"/>
-      <c r="K7" s="27"/>
-      <c r="L7" s="28"/>
-      <c r="M7" s="28"/>
-      <c r="N7" s="28"/>
-      <c r="O7" s="28"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="27"/>
+      <c r="N7" s="27"/>
+      <c r="O7" s="27"/>
       <c r="P7" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q7" s="27"/>
-      <c r="R7" s="28"/>
-      <c r="S7" s="28"/>
-      <c r="T7" s="28"/>
-      <c r="U7" s="28"/>
+      <c r="Q7" s="26"/>
+      <c r="R7" s="27"/>
+      <c r="S7" s="27"/>
+      <c r="T7" s="27"/>
+      <c r="U7" s="27"/>
       <c r="V7" s="15" t="s">
         <v>6</v>
       </c>
@@ -1101,11 +1105,11 @@
       <c r="X7" s="15"/>
       <c r="Y7" s="15"/>
       <c r="Z7" s="15"/>
-      <c r="AA7" s="27"/>
-      <c r="AB7" s="28"/>
-      <c r="AC7" s="28"/>
-      <c r="AD7" s="28"/>
-      <c r="AE7" s="28"/>
+      <c r="AA7" s="26"/>
+      <c r="AB7" s="27"/>
+      <c r="AC7" s="27"/>
+      <c r="AD7" s="27"/>
+      <c r="AE7" s="27"/>
       <c r="AF7" s="15" t="s">
         <v>27</v>
       </c>
@@ -1114,53 +1118,53 @@
       <c r="AI7" s="15"/>
       <c r="AJ7" s="15"/>
     </row>
-    <row r="8" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:55" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="29" t="s">
+    <row r="8" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="9" spans="1:55" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="37" t="s">
+      <c r="B9" s="28"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="38"/>
-      <c r="K9" s="38"/>
-      <c r="L9" s="38"/>
-      <c r="M9" s="38"/>
-      <c r="N9" s="39"/>
-      <c r="O9" s="29" t="s">
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="35"/>
+      <c r="K9" s="35"/>
+      <c r="L9" s="35"/>
+      <c r="M9" s="35"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="29"/>
-      <c r="R9" s="29"/>
-      <c r="S9" s="29"/>
-      <c r="T9" s="29"/>
-      <c r="U9" s="29"/>
-      <c r="V9" s="29" t="s">
+      <c r="P9" s="28"/>
+      <c r="Q9" s="28"/>
+      <c r="R9" s="28"/>
+      <c r="S9" s="28"/>
+      <c r="T9" s="28"/>
+      <c r="U9" s="28"/>
+      <c r="V9" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="W9" s="29"/>
-      <c r="X9" s="29"/>
-      <c r="Y9" s="29"/>
-      <c r="Z9" s="29"/>
-      <c r="AA9" s="29"/>
-      <c r="AB9" s="29"/>
-      <c r="AC9" s="33" t="s">
+      <c r="W9" s="28"/>
+      <c r="X9" s="28"/>
+      <c r="Y9" s="28"/>
+      <c r="Z9" s="28"/>
+      <c r="AA9" s="28"/>
+      <c r="AB9" s="28"/>
+      <c r="AC9" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="AD9" s="34"/>
-      <c r="AE9" s="34"/>
-      <c r="AF9" s="34"/>
-      <c r="AG9" s="34"/>
-      <c r="AH9" s="34"/>
-      <c r="AI9" s="35"/>
+      <c r="AD9" s="31"/>
+      <c r="AE9" s="31"/>
+      <c r="AF9" s="31"/>
+      <c r="AG9" s="31"/>
+      <c r="AH9" s="31"/>
+      <c r="AI9" s="32"/>
       <c r="AJ9" s="10"/>
       <c r="AK9" s="10"/>
       <c r="AL9" s="10"/>
@@ -1181,58 +1185,58 @@
       <c r="BA9" s="10"/>
       <c r="BB9" s="10"/>
     </row>
-    <row r="10" spans="1:55" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="29"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29" t="s">
+    <row r="10" spans="1:55" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="28"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="33" t="s">
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
+      <c r="K10" s="28"/>
+      <c r="L10" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="M10" s="34"/>
-      <c r="N10" s="35"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="32"/>
       <c r="O10" s="15" t="s">
         <v>8</v>
       </c>
       <c r="P10" s="15"/>
       <c r="Q10" s="15"/>
       <c r="R10" s="15"/>
-      <c r="S10" s="29" t="s">
+      <c r="S10" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="T10" s="29"/>
-      <c r="U10" s="29"/>
+      <c r="T10" s="28"/>
+      <c r="U10" s="28"/>
       <c r="V10" s="15" t="s">
         <v>8</v>
       </c>
       <c r="W10" s="15"/>
       <c r="X10" s="15"/>
       <c r="Y10" s="15"/>
-      <c r="Z10" s="29" t="s">
+      <c r="Z10" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="AA10" s="29"/>
-      <c r="AB10" s="29"/>
-      <c r="AC10" s="30" t="s">
+      <c r="AA10" s="28"/>
+      <c r="AB10" s="28"/>
+      <c r="AC10" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="AD10" s="31"/>
-      <c r="AE10" s="31"/>
-      <c r="AF10" s="32"/>
-      <c r="AG10" s="33" t="s">
+      <c r="AD10" s="53"/>
+      <c r="AE10" s="53"/>
+      <c r="AF10" s="54"/>
+      <c r="AG10" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="AH10" s="34"/>
-      <c r="AI10" s="35"/>
+      <c r="AH10" s="31"/>
+      <c r="AI10" s="32"/>
       <c r="AJ10" s="10"/>
       <c r="AK10" s="10"/>
       <c r="AL10" s="10"/>
@@ -1253,18 +1257,18 @@
       <c r="BA10" s="10"/>
       <c r="BB10" s="10"/>
     </row>
-    <row r="11" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="26"/>
-      <c r="K11" s="26"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="29"/>
       <c r="L11" s="18"/>
       <c r="M11" s="19"/>
       <c r="N11" s="20"/>
@@ -1309,18 +1313,18 @@
       <c r="BA11" s="10"/>
       <c r="BB11" s="10"/>
     </row>
-    <row r="12" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26"/>
-      <c r="K12" s="26"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="29"/>
+      <c r="K12" s="29"/>
       <c r="L12" s="18"/>
       <c r="M12" s="19"/>
       <c r="N12" s="20"/>
@@ -1366,18 +1370,18 @@
       <c r="BB12" s="10"/>
       <c r="BC12" s="10"/>
     </row>
-    <row r="13" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="26"/>
-      <c r="K13" s="26"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="29"/>
       <c r="L13" s="18"/>
       <c r="M13" s="19"/>
       <c r="N13" s="20"/>
@@ -1423,18 +1427,18 @@
       <c r="BB13" s="12"/>
       <c r="BC13" s="12"/>
     </row>
-    <row r="14" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="26"/>
-      <c r="K14" s="26"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="29"/>
       <c r="L14" s="18"/>
       <c r="M14" s="19"/>
       <c r="N14" s="20"/>
@@ -1480,18 +1484,18 @@
       <c r="BB14" s="10"/>
       <c r="BC14" s="10"/>
     </row>
-    <row r="15" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
-      <c r="K15" s="26"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
       <c r="L15" s="18"/>
       <c r="M15" s="19"/>
       <c r="N15" s="20"/>
@@ -1537,18 +1541,18 @@
       <c r="BB15" s="12"/>
       <c r="BC15" s="12"/>
     </row>
-    <row r="16" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="26"/>
-      <c r="K16" s="26"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="29"/>
       <c r="L16" s="18"/>
       <c r="M16" s="19"/>
       <c r="N16" s="20"/>
@@ -1594,18 +1598,18 @@
       <c r="BB16" s="10"/>
       <c r="BC16" s="10"/>
     </row>
-    <row r="17" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="26"/>
-      <c r="K17" s="26"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="29"/>
       <c r="L17" s="18"/>
       <c r="M17" s="19"/>
       <c r="N17" s="20"/>
@@ -1651,18 +1655,18 @@
       <c r="BB17" s="12"/>
       <c r="BC17" s="12"/>
     </row>
-    <row r="18" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="26"/>
-      <c r="K18" s="26"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="29"/>
+      <c r="K18" s="29"/>
       <c r="L18" s="18"/>
       <c r="M18" s="19"/>
       <c r="N18" s="20"/>
@@ -1708,18 +1712,18 @@
       <c r="BB18" s="10"/>
       <c r="BC18" s="10"/>
     </row>
-    <row r="19" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
-      <c r="K19" s="26"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="29"/>
+      <c r="K19" s="29"/>
       <c r="L19" s="18"/>
       <c r="M19" s="19"/>
       <c r="N19" s="20"/>
@@ -1765,18 +1769,18 @@
       <c r="BB19" s="10"/>
       <c r="BC19" s="10"/>
     </row>
-    <row r="20" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="26"/>
-      <c r="K20" s="26"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
+      <c r="K20" s="29"/>
       <c r="L20" s="18"/>
       <c r="M20" s="19"/>
       <c r="N20" s="20"/>
@@ -1822,18 +1826,18 @@
       <c r="BB20" s="10"/>
       <c r="BC20" s="10"/>
     </row>
-    <row r="21" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="26"/>
-      <c r="J21" s="26"/>
-      <c r="K21" s="26"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29"/>
+      <c r="I21" s="29"/>
+      <c r="J21" s="29"/>
+      <c r="K21" s="29"/>
       <c r="L21" s="18"/>
       <c r="M21" s="19"/>
       <c r="N21" s="20"/>
@@ -1879,18 +1883,18 @@
       <c r="BB21" s="10"/>
       <c r="BC21" s="10"/>
     </row>
-    <row r="22" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="26"/>
-      <c r="J22" s="26"/>
-      <c r="K22" s="26"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="29"/>
+      <c r="K22" s="29"/>
       <c r="L22" s="18"/>
       <c r="M22" s="19"/>
       <c r="N22" s="20"/>
@@ -1936,18 +1940,18 @@
       <c r="BB22" s="10"/>
       <c r="BC22" s="10"/>
     </row>
-    <row r="23" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
-      <c r="K23" s="26"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="29"/>
       <c r="L23" s="18"/>
       <c r="M23" s="19"/>
       <c r="N23" s="20"/>
@@ -1993,18 +1997,18 @@
       <c r="BB23" s="10"/>
       <c r="BC23" s="10"/>
     </row>
-    <row r="24" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="26"/>
-      <c r="K24" s="26"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="29"/>
+      <c r="K24" s="29"/>
       <c r="L24" s="18"/>
       <c r="M24" s="19"/>
       <c r="N24" s="20"/>
@@ -2050,18 +2054,18 @@
       <c r="BB24" s="10"/>
       <c r="BC24" s="10"/>
     </row>
-    <row r="25" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
-      <c r="C25" s="41"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
-      <c r="J25" s="26"/>
-      <c r="K25" s="26"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="29"/>
       <c r="L25" s="18"/>
       <c r="M25" s="19"/>
       <c r="N25" s="20"/>
@@ -2107,18 +2111,18 @@
       <c r="BB25" s="10"/>
       <c r="BC25" s="10"/>
     </row>
-    <row r="26" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="26"/>
-      <c r="K26" s="26"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="29"/>
       <c r="L26" s="18"/>
       <c r="M26" s="19"/>
       <c r="N26" s="20"/>
@@ -2164,18 +2168,18 @@
       <c r="BB26" s="10"/>
       <c r="BC26" s="10"/>
     </row>
-    <row r="27" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="26"/>
-      <c r="K27" s="26"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="29"/>
       <c r="L27" s="18"/>
       <c r="M27" s="19"/>
       <c r="N27" s="20"/>
@@ -2221,18 +2225,18 @@
       <c r="BB27" s="10"/>
       <c r="BC27" s="10"/>
     </row>
-    <row r="28" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="26"/>
-      <c r="J28" s="26"/>
-      <c r="K28" s="26"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="29"/>
       <c r="L28" s="18"/>
       <c r="M28" s="19"/>
       <c r="N28" s="20"/>
@@ -2278,18 +2282,18 @@
       <c r="BB28" s="10"/>
       <c r="BC28" s="10"/>
     </row>
-    <row r="29" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26"/>
-      <c r="K29" s="26"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
       <c r="L29" s="18"/>
       <c r="M29" s="19"/>
       <c r="N29" s="20"/>
@@ -2335,18 +2339,18 @@
       <c r="BB29" s="10"/>
       <c r="BC29" s="10"/>
     </row>
-    <row r="30" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="26"/>
-      <c r="J30" s="26"/>
-      <c r="K30" s="26"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="29"/>
       <c r="L30" s="18"/>
       <c r="M30" s="19"/>
       <c r="N30" s="20"/>
@@ -2392,18 +2396,18 @@
       <c r="BB30" s="10"/>
       <c r="BC30" s="10"/>
     </row>
-    <row r="31" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="26"/>
-      <c r="K31" s="26"/>
+      <c r="C31" s="39"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="29"/>
+      <c r="K31" s="29"/>
       <c r="L31" s="18"/>
       <c r="M31" s="19"/>
       <c r="N31" s="20"/>
@@ -2449,18 +2453,18 @@
       <c r="BB31" s="10"/>
       <c r="BC31" s="10"/>
     </row>
-    <row r="32" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="6"/>
       <c r="B32" s="6"/>
-      <c r="C32" s="41"/>
-      <c r="D32" s="41"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="26"/>
-      <c r="I32" s="26"/>
-      <c r="J32" s="26"/>
-      <c r="K32" s="26"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="29"/>
       <c r="L32" s="18"/>
       <c r="M32" s="19"/>
       <c r="N32" s="20"/>
@@ -2506,18 +2510,18 @@
       <c r="BB32" s="10"/>
       <c r="BC32" s="10"/>
     </row>
-    <row r="33" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="6"/>
       <c r="B33" s="6"/>
-      <c r="C33" s="41"/>
-      <c r="D33" s="41"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="26"/>
-      <c r="J33" s="26"/>
-      <c r="K33" s="26"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29"/>
+      <c r="I33" s="29"/>
+      <c r="J33" s="29"/>
+      <c r="K33" s="29"/>
       <c r="L33" s="18"/>
       <c r="M33" s="19"/>
       <c r="N33" s="20"/>
@@ -2563,18 +2567,18 @@
       <c r="BB33" s="10"/>
       <c r="BC33" s="10"/>
     </row>
-    <row r="34" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="6"/>
       <c r="B34" s="6"/>
-      <c r="C34" s="41"/>
-      <c r="D34" s="41"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="26"/>
-      <c r="J34" s="26"/>
-      <c r="K34" s="26"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29"/>
+      <c r="I34" s="29"/>
+      <c r="J34" s="29"/>
+      <c r="K34" s="29"/>
       <c r="L34" s="18"/>
       <c r="M34" s="19"/>
       <c r="N34" s="20"/>
@@ -2620,18 +2624,18 @@
       <c r="BB34" s="10"/>
       <c r="BC34" s="10"/>
     </row>
-    <row r="35" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
-      <c r="C35" s="41"/>
-      <c r="D35" s="41"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="26"/>
-      <c r="J35" s="26"/>
-      <c r="K35" s="26"/>
+      <c r="C35" s="39"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="29"/>
+      <c r="I35" s="29"/>
+      <c r="J35" s="29"/>
+      <c r="K35" s="29"/>
       <c r="L35" s="18"/>
       <c r="M35" s="19"/>
       <c r="N35" s="20"/>
@@ -2677,18 +2681,18 @@
       <c r="BB35" s="10"/>
       <c r="BC35" s="10"/>
     </row>
-    <row r="36" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="6"/>
       <c r="B36" s="6"/>
-      <c r="C36" s="41"/>
-      <c r="D36" s="41"/>
-      <c r="E36" s="26"/>
-      <c r="F36" s="26"/>
-      <c r="G36" s="26"/>
-      <c r="H36" s="26"/>
-      <c r="I36" s="26"/>
-      <c r="J36" s="26"/>
-      <c r="K36" s="26"/>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="29"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="29"/>
+      <c r="I36" s="29"/>
+      <c r="J36" s="29"/>
+      <c r="K36" s="29"/>
       <c r="L36" s="18"/>
       <c r="M36" s="19"/>
       <c r="N36" s="20"/>
@@ -2734,18 +2738,18 @@
       <c r="BB36" s="10"/>
       <c r="BC36" s="10"/>
     </row>
-    <row r="37" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
-      <c r="C37" s="41"/>
-      <c r="D37" s="41"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="26"/>
-      <c r="J37" s="26"/>
-      <c r="K37" s="26"/>
+      <c r="C37" s="39"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="29"/>
+      <c r="K37" s="29"/>
       <c r="L37" s="18"/>
       <c r="M37" s="19"/>
       <c r="N37" s="20"/>
@@ -2791,18 +2795,18 @@
       <c r="BB37" s="10"/>
       <c r="BC37" s="10"/>
     </row>
-    <row r="38" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="6"/>
       <c r="B38" s="6"/>
-      <c r="C38" s="41"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="26"/>
-      <c r="F38" s="26"/>
-      <c r="G38" s="26"/>
-      <c r="H38" s="26"/>
-      <c r="I38" s="26"/>
-      <c r="J38" s="26"/>
-      <c r="K38" s="26"/>
+      <c r="C38" s="39"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="29"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="29"/>
+      <c r="I38" s="29"/>
+      <c r="J38" s="29"/>
+      <c r="K38" s="29"/>
       <c r="L38" s="18"/>
       <c r="M38" s="19"/>
       <c r="N38" s="20"/>
@@ -2848,18 +2852,18 @@
       <c r="BB38" s="10"/>
       <c r="BC38" s="10"/>
     </row>
-    <row r="39" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="6"/>
       <c r="B39" s="6"/>
-      <c r="C39" s="41"/>
-      <c r="D39" s="41"/>
-      <c r="E39" s="26"/>
-      <c r="F39" s="26"/>
-      <c r="G39" s="26"/>
-      <c r="H39" s="26"/>
-      <c r="I39" s="26"/>
-      <c r="J39" s="26"/>
-      <c r="K39" s="26"/>
+      <c r="C39" s="39"/>
+      <c r="D39" s="39"/>
+      <c r="E39" s="29"/>
+      <c r="F39" s="29"/>
+      <c r="G39" s="29"/>
+      <c r="H39" s="29"/>
+      <c r="I39" s="29"/>
+      <c r="J39" s="29"/>
+      <c r="K39" s="29"/>
       <c r="L39" s="18"/>
       <c r="M39" s="19"/>
       <c r="N39" s="20"/>
@@ -2905,18 +2909,18 @@
       <c r="BB39" s="10"/>
       <c r="BC39" s="10"/>
     </row>
-    <row r="40" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="6"/>
       <c r="B40" s="6"/>
-      <c r="C40" s="41"/>
-      <c r="D40" s="41"/>
-      <c r="E40" s="26"/>
-      <c r="F40" s="26"/>
-      <c r="G40" s="26"/>
-      <c r="H40" s="26"/>
-      <c r="I40" s="26"/>
-      <c r="J40" s="26"/>
-      <c r="K40" s="26"/>
+      <c r="C40" s="39"/>
+      <c r="D40" s="39"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="29"/>
+      <c r="I40" s="29"/>
+      <c r="J40" s="29"/>
+      <c r="K40" s="29"/>
       <c r="L40" s="18"/>
       <c r="M40" s="19"/>
       <c r="N40" s="20"/>
@@ -2962,18 +2966,18 @@
       <c r="BB40" s="10"/>
       <c r="BC40" s="10"/>
     </row>
-    <row r="41" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
-      <c r="C41" s="41"/>
-      <c r="D41" s="41"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="26"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="26"/>
-      <c r="J41" s="26"/>
-      <c r="K41" s="26"/>
+      <c r="C41" s="39"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="29"/>
+      <c r="H41" s="29"/>
+      <c r="I41" s="29"/>
+      <c r="J41" s="29"/>
+      <c r="K41" s="29"/>
       <c r="L41" s="18"/>
       <c r="M41" s="19"/>
       <c r="N41" s="20"/>
@@ -3019,7 +3023,7 @@
       <c r="BB41" s="10"/>
       <c r="BC41" s="10"/>
     </row>
-    <row r="42" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="3"/>
@@ -3066,35 +3070,35 @@
       <c r="AR42" s="4"/>
       <c r="AS42" s="4"/>
     </row>
-    <row r="43" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="29" t="s">
+    <row r="43" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="B43" s="29"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29" t="s">
+      <c r="B43" s="28"/>
+      <c r="C43" s="28"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="28"/>
+      <c r="F43" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="G43" s="29"/>
-      <c r="H43" s="29"/>
-      <c r="I43" s="29" t="s">
+      <c r="G43" s="28"/>
+      <c r="H43" s="28"/>
+      <c r="I43" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="J43" s="29"/>
-      <c r="K43" s="29"/>
-      <c r="L43" s="29" t="s">
+      <c r="J43" s="28"/>
+      <c r="K43" s="28"/>
+      <c r="L43" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="M43" s="29"/>
-      <c r="N43" s="29"/>
-      <c r="O43" s="29" t="s">
+      <c r="M43" s="28"/>
+      <c r="N43" s="28"/>
+      <c r="O43" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="P43" s="29"/>
-      <c r="Q43" s="29"/>
-      <c r="R43" s="29"/>
+      <c r="P43" s="28"/>
+      <c r="Q43" s="28"/>
+      <c r="R43" s="28"/>
       <c r="AE43" s="17" t="s">
         <v>28</v>
       </c>
@@ -3122,27 +3126,27 @@
       <c r="BA43" s="17"/>
       <c r="BB43" s="17"/>
     </row>
-    <row r="44" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="29" t="s">
+    <row r="44" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A44" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="B44" s="29"/>
-      <c r="C44" s="29"/>
-      <c r="D44" s="29"/>
-      <c r="E44" s="29"/>
-      <c r="F44" s="40"/>
-      <c r="G44" s="41"/>
-      <c r="H44" s="41"/>
-      <c r="I44" s="40"/>
-      <c r="J44" s="41"/>
-      <c r="K44" s="41"/>
-      <c r="L44" s="42"/>
-      <c r="M44" s="43"/>
-      <c r="N44" s="43"/>
-      <c r="O44" s="13"/>
-      <c r="P44" s="13"/>
-      <c r="Q44" s="13"/>
-      <c r="R44" s="13"/>
+      <c r="B44" s="28"/>
+      <c r="C44" s="28"/>
+      <c r="D44" s="28"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="38"/>
+      <c r="G44" s="39"/>
+      <c r="H44" s="39"/>
+      <c r="I44" s="38"/>
+      <c r="J44" s="39"/>
+      <c r="K44" s="39"/>
+      <c r="L44" s="40"/>
+      <c r="M44" s="37"/>
+      <c r="N44" s="37"/>
+      <c r="O44" s="37"/>
+      <c r="P44" s="37"/>
+      <c r="Q44" s="37"/>
+      <c r="R44" s="37"/>
       <c r="AE44" s="16"/>
       <c r="AF44" s="16"/>
       <c r="AG44" s="16"/>
@@ -3168,27 +3172,27 @@
       <c r="BA44" s="16"/>
       <c r="BB44" s="16"/>
     </row>
-    <row r="45" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="29" t="s">
+    <row r="45" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="B45" s="29"/>
-      <c r="C45" s="29"/>
-      <c r="D45" s="29"/>
-      <c r="E45" s="29"/>
-      <c r="F45" s="40"/>
-      <c r="G45" s="41"/>
-      <c r="H45" s="41"/>
-      <c r="I45" s="40"/>
-      <c r="J45" s="41"/>
-      <c r="K45" s="41"/>
-      <c r="L45" s="42"/>
-      <c r="M45" s="43"/>
-      <c r="N45" s="43"/>
-      <c r="O45" s="13"/>
-      <c r="P45" s="13"/>
-      <c r="Q45" s="13"/>
-      <c r="R45" s="13"/>
+      <c r="B45" s="28"/>
+      <c r="C45" s="28"/>
+      <c r="D45" s="28"/>
+      <c r="E45" s="28"/>
+      <c r="F45" s="38"/>
+      <c r="G45" s="39"/>
+      <c r="H45" s="39"/>
+      <c r="I45" s="38"/>
+      <c r="J45" s="39"/>
+      <c r="K45" s="39"/>
+      <c r="L45" s="40"/>
+      <c r="M45" s="37"/>
+      <c r="N45" s="37"/>
+      <c r="O45" s="37"/>
+      <c r="P45" s="37"/>
+      <c r="Q45" s="37"/>
+      <c r="R45" s="37"/>
       <c r="AE45" s="16"/>
       <c r="AF45" s="16"/>
       <c r="AG45" s="16"/>
@@ -3214,27 +3218,27 @@
       <c r="BA45" s="16"/>
       <c r="BB45" s="16"/>
     </row>
-    <row r="46" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="29" t="s">
+    <row r="46" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A46" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="B46" s="29"/>
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="40"/>
-      <c r="G46" s="41"/>
-      <c r="H46" s="41"/>
-      <c r="I46" s="40"/>
-      <c r="J46" s="41"/>
-      <c r="K46" s="41"/>
-      <c r="L46" s="42"/>
-      <c r="M46" s="43"/>
-      <c r="N46" s="43"/>
-      <c r="O46" s="13"/>
-      <c r="P46" s="13"/>
-      <c r="Q46" s="13"/>
-      <c r="R46" s="13"/>
+      <c r="B46" s="28"/>
+      <c r="C46" s="28"/>
+      <c r="D46" s="28"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="38"/>
+      <c r="G46" s="39"/>
+      <c r="H46" s="39"/>
+      <c r="I46" s="38"/>
+      <c r="J46" s="39"/>
+      <c r="K46" s="39"/>
+      <c r="L46" s="40"/>
+      <c r="M46" s="37"/>
+      <c r="N46" s="37"/>
+      <c r="O46" s="37"/>
+      <c r="P46" s="37"/>
+      <c r="Q46" s="37"/>
+      <c r="R46" s="37"/>
       <c r="AE46" s="16"/>
       <c r="AF46" s="16"/>
       <c r="AG46" s="16"/>
@@ -3260,27 +3264,27 @@
       <c r="BA46" s="16"/>
       <c r="BB46" s="16"/>
     </row>
-    <row r="47" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="29" t="s">
+    <row r="47" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A47" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="B47" s="29"/>
-      <c r="C47" s="29"/>
-      <c r="D47" s="29"/>
-      <c r="E47" s="29"/>
-      <c r="F47" s="40"/>
-      <c r="G47" s="41"/>
-      <c r="H47" s="41"/>
-      <c r="I47" s="40"/>
-      <c r="J47" s="41"/>
-      <c r="K47" s="41"/>
-      <c r="L47" s="42"/>
-      <c r="M47" s="43"/>
-      <c r="N47" s="43"/>
-      <c r="O47" s="13"/>
-      <c r="P47" s="13"/>
-      <c r="Q47" s="13"/>
-      <c r="R47" s="13"/>
+      <c r="B47" s="28"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="28"/>
+      <c r="E47" s="28"/>
+      <c r="F47" s="38"/>
+      <c r="G47" s="39"/>
+      <c r="H47" s="39"/>
+      <c r="I47" s="38"/>
+      <c r="J47" s="39"/>
+      <c r="K47" s="39"/>
+      <c r="L47" s="40"/>
+      <c r="M47" s="37"/>
+      <c r="N47" s="37"/>
+      <c r="O47" s="37"/>
+      <c r="P47" s="37"/>
+      <c r="Q47" s="37"/>
+      <c r="R47" s="37"/>
       <c r="AE47" s="16"/>
       <c r="AF47" s="16"/>
       <c r="AG47" s="16"/>
@@ -3306,93 +3310,93 @@
       <c r="BA47" s="16"/>
       <c r="BB47" s="16"/>
     </row>
-    <row r="48" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="29" t="s">
+    <row r="48" spans="1:55" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A48" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="B48" s="29"/>
-      <c r="C48" s="29"/>
-      <c r="D48" s="29"/>
-      <c r="E48" s="29"/>
-      <c r="F48" s="40"/>
-      <c r="G48" s="41"/>
-      <c r="H48" s="41"/>
-      <c r="I48" s="40"/>
-      <c r="J48" s="41"/>
-      <c r="K48" s="41"/>
-      <c r="L48" s="42"/>
-      <c r="M48" s="43"/>
-      <c r="N48" s="43"/>
-      <c r="O48" s="13"/>
-      <c r="P48" s="13"/>
-      <c r="Q48" s="13"/>
-      <c r="R48" s="13"/>
-    </row>
-    <row r="49" spans="1:35" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="29" t="s">
+      <c r="B48" s="28"/>
+      <c r="C48" s="28"/>
+      <c r="D48" s="28"/>
+      <c r="E48" s="28"/>
+      <c r="F48" s="38"/>
+      <c r="G48" s="39"/>
+      <c r="H48" s="39"/>
+      <c r="I48" s="38"/>
+      <c r="J48" s="39"/>
+      <c r="K48" s="39"/>
+      <c r="L48" s="40"/>
+      <c r="M48" s="37"/>
+      <c r="N48" s="37"/>
+      <c r="O48" s="37"/>
+      <c r="P48" s="37"/>
+      <c r="Q48" s="37"/>
+      <c r="R48" s="37"/>
+    </row>
+    <row r="49" spans="1:35" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A49" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="B49" s="29"/>
-      <c r="C49" s="29"/>
-      <c r="D49" s="29"/>
-      <c r="E49" s="29"/>
-      <c r="F49" s="40"/>
-      <c r="G49" s="41"/>
-      <c r="H49" s="41"/>
-      <c r="I49" s="40"/>
-      <c r="J49" s="41"/>
-      <c r="K49" s="41"/>
-      <c r="L49" s="42"/>
-      <c r="M49" s="43"/>
-      <c r="N49" s="43"/>
-      <c r="O49" s="13"/>
-      <c r="P49" s="13"/>
-      <c r="Q49" s="13"/>
-      <c r="R49" s="13"/>
-    </row>
-    <row r="50" spans="1:35" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="29" t="s">
+      <c r="B49" s="28"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="28"/>
+      <c r="E49" s="28"/>
+      <c r="F49" s="38"/>
+      <c r="G49" s="39"/>
+      <c r="H49" s="39"/>
+      <c r="I49" s="38"/>
+      <c r="J49" s="39"/>
+      <c r="K49" s="39"/>
+      <c r="L49" s="40"/>
+      <c r="M49" s="37"/>
+      <c r="N49" s="37"/>
+      <c r="O49" s="37"/>
+      <c r="P49" s="37"/>
+      <c r="Q49" s="37"/>
+      <c r="R49" s="37"/>
+    </row>
+    <row r="50" spans="1:35" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A50" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="B50" s="29"/>
-      <c r="C50" s="29"/>
-      <c r="D50" s="29"/>
-      <c r="E50" s="29"/>
-      <c r="F50" s="40"/>
-      <c r="G50" s="41"/>
-      <c r="H50" s="41"/>
-      <c r="I50" s="40"/>
-      <c r="J50" s="41"/>
-      <c r="K50" s="41"/>
-      <c r="L50" s="42"/>
-      <c r="M50" s="43"/>
-      <c r="N50" s="43"/>
-      <c r="O50" s="13"/>
-      <c r="P50" s="13"/>
-      <c r="Q50" s="13"/>
-      <c r="R50" s="13"/>
-    </row>
-    <row r="51" spans="1:35" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="29" t="s">
+      <c r="B50" s="28"/>
+      <c r="C50" s="28"/>
+      <c r="D50" s="28"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="38"/>
+      <c r="G50" s="39"/>
+      <c r="H50" s="39"/>
+      <c r="I50" s="38"/>
+      <c r="J50" s="39"/>
+      <c r="K50" s="39"/>
+      <c r="L50" s="40"/>
+      <c r="M50" s="37"/>
+      <c r="N50" s="37"/>
+      <c r="O50" s="37"/>
+      <c r="P50" s="37"/>
+      <c r="Q50" s="37"/>
+      <c r="R50" s="37"/>
+    </row>
+    <row r="51" spans="1:35" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A51" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B51" s="29"/>
-      <c r="C51" s="29"/>
-      <c r="D51" s="29"/>
-      <c r="E51" s="29"/>
-      <c r="F51" s="40"/>
-      <c r="G51" s="41"/>
-      <c r="H51" s="41"/>
-      <c r="I51" s="40"/>
-      <c r="J51" s="41"/>
-      <c r="K51" s="41"/>
-      <c r="L51" s="42"/>
-      <c r="M51" s="43"/>
-      <c r="N51" s="43"/>
-      <c r="O51" s="13"/>
-      <c r="P51" s="13"/>
-      <c r="Q51" s="13"/>
-      <c r="R51" s="13"/>
+      <c r="B51" s="28"/>
+      <c r="C51" s="28"/>
+      <c r="D51" s="28"/>
+      <c r="E51" s="28"/>
+      <c r="F51" s="38"/>
+      <c r="G51" s="39"/>
+      <c r="H51" s="39"/>
+      <c r="I51" s="38"/>
+      <c r="J51" s="39"/>
+      <c r="K51" s="39"/>
+      <c r="L51" s="40"/>
+      <c r="M51" s="37"/>
+      <c r="N51" s="37"/>
+      <c r="O51" s="37"/>
+      <c r="P51" s="37"/>
+      <c r="Q51" s="37"/>
+      <c r="R51" s="37"/>
       <c r="AE51" s="14" t="s">
         <v>24</v>
       </c>
@@ -3401,27 +3405,27 @@
       <c r="AH51" s="14"/>
       <c r="AI51" s="14"/>
     </row>
-    <row r="52" spans="1:35" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="29" t="s">
+    <row r="52" spans="1:35" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A52" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B52" s="29"/>
-      <c r="C52" s="29"/>
-      <c r="D52" s="29"/>
-      <c r="E52" s="29"/>
-      <c r="F52" s="40"/>
-      <c r="G52" s="41"/>
-      <c r="H52" s="41"/>
-      <c r="I52" s="40"/>
-      <c r="J52" s="41"/>
-      <c r="K52" s="41"/>
-      <c r="L52" s="42"/>
-      <c r="M52" s="43"/>
-      <c r="N52" s="43"/>
-      <c r="O52" s="13"/>
-      <c r="P52" s="13"/>
-      <c r="Q52" s="13"/>
-      <c r="R52" s="13"/>
+      <c r="B52" s="28"/>
+      <c r="C52" s="28"/>
+      <c r="D52" s="28"/>
+      <c r="E52" s="28"/>
+      <c r="F52" s="38"/>
+      <c r="G52" s="39"/>
+      <c r="H52" s="39"/>
+      <c r="I52" s="38"/>
+      <c r="J52" s="39"/>
+      <c r="K52" s="39"/>
+      <c r="L52" s="40"/>
+      <c r="M52" s="37"/>
+      <c r="N52" s="37"/>
+      <c r="O52" s="37"/>
+      <c r="P52" s="37"/>
+      <c r="Q52" s="37"/>
+      <c r="R52" s="37"/>
       <c r="AE52" s="13"/>
       <c r="AF52" s="13"/>
       <c r="AG52" s="13"/>
@@ -3450,6 +3454,10 @@
     <mergeCell ref="A9:D10"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
+    <mergeCell ref="AC10:AF10"/>
+    <mergeCell ref="AC11:AF11"/>
+    <mergeCell ref="AG11:AI11"/>
+    <mergeCell ref="AG10:AI10"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="C21:D21"/>
@@ -3459,6 +3467,18 @@
     <mergeCell ref="S18:U18"/>
     <mergeCell ref="V18:Y18"/>
     <mergeCell ref="Z18:AB18"/>
+    <mergeCell ref="E19:K19"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="O19:R19"/>
+    <mergeCell ref="S19:U19"/>
+    <mergeCell ref="V19:Y19"/>
+    <mergeCell ref="Z19:AB19"/>
+    <mergeCell ref="E21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O21:R21"/>
+    <mergeCell ref="S21:U21"/>
+    <mergeCell ref="V21:Y21"/>
+    <mergeCell ref="Z21:AB21"/>
     <mergeCell ref="E24:K24"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="O24:R24"/>
@@ -3607,6 +3627,8 @@
     <mergeCell ref="C41:D41"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="C39:D39"/>
+    <mergeCell ref="E41:K41"/>
+    <mergeCell ref="E39:K39"/>
     <mergeCell ref="A51:E51"/>
     <mergeCell ref="A52:E52"/>
     <mergeCell ref="F43:H43"/>
@@ -3650,10 +3672,6 @@
     <mergeCell ref="O50:R50"/>
     <mergeCell ref="O51:R51"/>
     <mergeCell ref="O52:R52"/>
-    <mergeCell ref="AC10:AF10"/>
-    <mergeCell ref="AC11:AF11"/>
-    <mergeCell ref="AG11:AI11"/>
-    <mergeCell ref="AG10:AI10"/>
     <mergeCell ref="AC9:AI9"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A5:J5"/>
@@ -3713,12 +3731,6 @@
     <mergeCell ref="Z17:AB17"/>
     <mergeCell ref="AC17:AF17"/>
     <mergeCell ref="AG17:AI17"/>
-    <mergeCell ref="E19:K19"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="O19:R19"/>
-    <mergeCell ref="S19:U19"/>
-    <mergeCell ref="V19:Y19"/>
-    <mergeCell ref="Z19:AB19"/>
     <mergeCell ref="AC19:AF19"/>
     <mergeCell ref="AG19:AI19"/>
     <mergeCell ref="E20:K20"/>
@@ -3729,12 +3741,6 @@
     <mergeCell ref="Z20:AB20"/>
     <mergeCell ref="AC20:AF20"/>
     <mergeCell ref="AG20:AI20"/>
-    <mergeCell ref="E21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O21:R21"/>
-    <mergeCell ref="S21:U21"/>
-    <mergeCell ref="V21:Y21"/>
-    <mergeCell ref="Z21:AB21"/>
     <mergeCell ref="AC21:AF21"/>
     <mergeCell ref="AG21:AI21"/>
     <mergeCell ref="E22:K22"/>
@@ -3745,7 +3751,6 @@
     <mergeCell ref="Z22:AB22"/>
     <mergeCell ref="AC22:AF22"/>
     <mergeCell ref="AG22:AI22"/>
-    <mergeCell ref="E41:K41"/>
     <mergeCell ref="L41:N41"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="S41:U41"/>
@@ -3758,7 +3763,6 @@
     <mergeCell ref="Z38:AB38"/>
     <mergeCell ref="AC38:AF38"/>
     <mergeCell ref="AG38:AI38"/>
-    <mergeCell ref="E39:K39"/>
     <mergeCell ref="L39:N39"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="S39:U39"/>
